--- a/output/stock_quant_scores/GOOGL_balance_df.xlsx
+++ b/output/stock_quant_scores/GOOGL_balance_df.xlsx
@@ -993,7 +993,9 @@
       <c r="BO2" t="n">
         <v>15714000000</v>
       </c>
-      <c r="BP2" t="inlineStr"/>
+      <c r="BP2" t="n">
+        <v>2670000000</v>
+      </c>
       <c r="BQ2" t="n">
         <v>52340000000</v>
       </c>
@@ -1215,7 +1217,9 @@
       <c r="BO3" t="n">
         <v>12650000000</v>
       </c>
-      <c r="BP3" t="inlineStr"/>
+      <c r="BP3" t="n">
+        <v>2670000000</v>
+      </c>
       <c r="BQ3" t="n">
         <v>47964000000</v>
       </c>
@@ -1694,23 +1698,33 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>28395000000</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>123889000000</v>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>251635000000</v>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>191484000000</v>
+      </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" t="n">
+        <v>107633000000</v>
+      </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
@@ -1726,7 +1740,9 @@
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>64254000000</v>
+      </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
@@ -1742,7 +1758,9 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>359268000000</v>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="inlineStr"/>
@@ -1773,7 +1791,9 @@
         <v>49732000000</v>
       </c>
       <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr"/>
+      <c r="BN6" t="n">
+        <v>188143000000</v>
+      </c>
       <c r="BO6" t="inlineStr"/>
       <c r="BP6" t="n">
         <v>728000000</v>
@@ -1787,7 +1807,9 @@
       <c r="BU6" t="inlineStr"/>
       <c r="BV6" t="inlineStr"/>
       <c r="BW6" t="inlineStr"/>
-      <c r="BX6" t="inlineStr"/>
+      <c r="BX6" t="n">
+        <v>20945000000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
